--- a/APOYO_MAT_LISTADO_FICHAS_PRUEBAS.xlsx
+++ b/APOYO_MAT_LISTADO_FICHAS_PRUEBAS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AGP\Desktop\2 eso\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F03597FA-89DF-4FA4-968B-A4696C446A70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0D387AC-4D33-4ACB-A366-03690A6913F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{051C6437-CF6D-435E-ACB8-F6B20B0C248C}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="94">
   <si>
     <t>CODIGO</t>
   </si>
@@ -304,6 +304,12 @@
   </si>
   <si>
     <t>254P - 2º ESO - FRACCIONES - RESOLUCIÓN DE PROBLEMAS CON FRACCIONES</t>
+  </si>
+  <si>
+    <t>MATERIAL</t>
+  </si>
+  <si>
+    <t>PRUEBA</t>
   </si>
 </sst>
 </file>
@@ -693,532 +699,617 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE4216F7-0C51-4F64-B136-9F38940C606F}">
-  <dimension ref="A1:F28"/>
+  <dimension ref="A1:G28"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="7.77734375" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.33203125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="20" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="51.6640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="85.21875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.77734375" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.33203125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="20" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="51.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="85.21875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.6640625" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="C1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="D1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="E1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="F1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="G1" s="2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="B2" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="E2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="F2" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="4"/>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G2" s="4"/>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="B3" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D3" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="E3" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="F3" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="F3" s="4"/>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G3" s="4"/>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="B4" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="B4" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="E4" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="F4" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="F4" s="4"/>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G4" s="4"/>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="B5" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="B5" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D5" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="E5" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="F5" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="F5" s="4"/>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G5" s="4"/>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="B6" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="B6" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C6" s="3" t="s">
+      <c r="C6" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D6" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="E6" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="E6" s="3" t="s">
+      <c r="F6" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="F6" s="4"/>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G6" s="4"/>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="B7" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="B7" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C7" s="3" t="s">
+      <c r="C7" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D7" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="E7" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="E7" s="3" t="s">
+      <c r="F7" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="F7" s="4"/>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G7" s="4"/>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="B8" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="B8" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C8" s="3" t="s">
+      <c r="C8" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D8" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="D8" s="3" t="s">
+      <c r="E8" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="E8" s="3" t="s">
+      <c r="F8" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="F8" s="4"/>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G8" s="4"/>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="B9" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="B9" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C9" s="3" t="s">
+      <c r="C9" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D9" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="D9" s="3" t="s">
+      <c r="E9" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="E9" s="3" t="s">
+      <c r="F9" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="F9" s="4"/>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G9" s="4"/>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="B10" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="B10" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C10" s="3" t="s">
+      <c r="C10" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D10" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="D10" s="3" t="s">
+      <c r="E10" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="E10" s="3" t="s">
+      <c r="F10" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="F10" s="4"/>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G10" s="4"/>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="B11" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="B11" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C11" s="3" t="s">
+      <c r="C11" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D11" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="D11" s="3" t="s">
+      <c r="E11" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="E11" s="3" t="s">
+      <c r="F11" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="F11" s="4"/>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G11" s="4"/>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="B12" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="B12" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C12" s="3" t="s">
+      <c r="C12" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D12" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="D12" s="3" t="s">
+      <c r="E12" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="E12" s="3" t="s">
+      <c r="F12" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="F12" s="4"/>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G12" s="4"/>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="B13" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="B13" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C13" s="3" t="s">
+      <c r="C13" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D13" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="D13" s="3" t="s">
+      <c r="E13" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="E13" s="3" t="s">
+      <c r="F13" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="F13" s="4">
+      <c r="G13" s="4">
         <v>20</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="B14" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="B14" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>46</v>
+      <c r="C14" s="4" t="s">
+        <v>7</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>46</v>
       </c>
       <c r="E14" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F14" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="F14" s="4"/>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G14" s="4"/>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="B15" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="B15" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C15" s="3" t="s">
+      <c r="C15" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D15" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="D15" s="3" t="s">
+      <c r="E15" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="E15" s="3" t="s">
+      <c r="F15" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="F15" s="4"/>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G15" s="4"/>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="B16" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="B16" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C16" s="3" t="s">
+      <c r="C16" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D16" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="D16" s="3" t="s">
+      <c r="E16" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="E16" s="3" t="s">
+      <c r="F16" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="F16" s="4"/>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G16" s="4"/>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="B17" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="B17" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C17" s="3" t="s">
+      <c r="C17" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D17" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="D17" s="3" t="s">
+      <c r="E17" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="E17" s="3" t="s">
+      <c r="F17" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="F17" s="4"/>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G17" s="4"/>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="B18" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="B18" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C18" s="3" t="s">
+      <c r="C18" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D18" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="D18" s="3" t="s">
+      <c r="E18" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="E18" s="3" t="s">
+      <c r="F18" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="F18" s="4">
+      <c r="G18" s="4">
         <v>19</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="B19" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="B19" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C19" s="3" t="s">
+      <c r="C19" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D19" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="D19" s="3" t="s">
+      <c r="E19" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="E19" s="3" t="s">
+      <c r="F19" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="F19" s="4"/>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G19" s="4"/>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="B20" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="B20" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C20" s="3" t="s">
+      <c r="C20" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D20" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="D20" s="3" t="s">
+      <c r="E20" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="E20" s="3" t="s">
+      <c r="F20" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="F20" s="4"/>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G20" s="4"/>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="B21" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="B21" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C21" s="3" t="s">
+      <c r="C21" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D21" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="D21" s="3" t="s">
+      <c r="E21" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="E21" s="3" t="s">
+      <c r="F21" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="F21" s="4"/>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G21" s="4"/>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="B22" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="B22" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C22" s="3" t="s">
+      <c r="C22" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D22" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="D22" s="3" t="s">
+      <c r="E22" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="E22" s="3" t="s">
+      <c r="F22" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="F22" s="4"/>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G22" s="4"/>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="B23" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="B23" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C23" s="3" t="s">
+      <c r="C23" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D23" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="D23" s="3" t="s">
+      <c r="E23" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="E23" s="3" t="s">
+      <c r="F23" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="F23" s="4"/>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G23" s="4"/>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="B24" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="B24" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C24" s="3" t="s">
+      <c r="C24" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D24" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="D24" s="3" t="s">
+      <c r="E24" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="E24" s="3" t="s">
+      <c r="F24" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="F24" s="4"/>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G24" s="4"/>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="B25" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="B25" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C25" s="3" t="s">
+      <c r="C25" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D25" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="D25" s="3" t="s">
+      <c r="E25" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="E25" s="3" t="s">
+      <c r="F25" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="F25" s="4">
+      <c r="G25" s="4">
         <v>15</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="B26" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="B26" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C26" s="3" t="s">
+      <c r="C26" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D26" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="D26" s="3" t="s">
+      <c r="E26" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="E26" s="3" t="s">
+      <c r="F26" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="F26" s="4">
+      <c r="G26" s="4">
         <v>15</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="B27" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="B27" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C27" s="3" t="s">
+      <c r="C27" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D27" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="D27" s="3" t="s">
+      <c r="E27" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="E27" s="3" t="s">
+      <c r="F27" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="F27" s="4">
+      <c r="G27" s="4">
         <v>14</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="B28" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="B28" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C28" s="3" t="s">
+      <c r="C28" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D28" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="D28" s="3" t="s">
+      <c r="E28" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="E28" s="3" t="s">
+      <c r="F28" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="F28" s="4">
+      <c r="G28" s="4">
         <v>20</v>
       </c>
     </row>

--- a/APOYO_MAT_LISTADO_FICHAS_PRUEBAS.xlsx
+++ b/APOYO_MAT_LISTADO_FICHAS_PRUEBAS.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AGP\Desktop\2 eso\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AGP\Desktop\APOYO-MAT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0D387AC-4D33-4ACB-A366-03690A6913F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBC495B7-B220-4A31-9E62-A341D805FE98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{051C6437-CF6D-435E-ACB8-F6B20B0C248C}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="99">
   <si>
     <t>CODIGO</t>
   </si>
@@ -310,6 +310,21 @@
   </si>
   <si>
     <t>PRUEBA</t>
+  </si>
+  <si>
+    <t>0654P</t>
+  </si>
+  <si>
+    <t>0531F</t>
+  </si>
+  <si>
+    <t>0416E</t>
+  </si>
+  <si>
+    <t>ESQUEMA</t>
+  </si>
+  <si>
+    <t>FICHA</t>
   </si>
 </sst>
 </file>
@@ -699,7 +714,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE4216F7-0C51-4F64-B136-9F38940C606F}">
-  <dimension ref="A1:G28"/>
+  <dimension ref="A1:G31"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.44140625" style="1" bestFit="1" customWidth="1"/>
@@ -1313,6 +1328,75 @@
         <v>20</v>
       </c>
     </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A29" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="F29" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="G29" s="4">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A30" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="F30" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="G30" s="4">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A31" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="F31" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="G31" s="4">
+        <v>20</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/APOYO_MAT_LISTADO_FICHAS_PRUEBAS.xlsx
+++ b/APOYO_MAT_LISTADO_FICHAS_PRUEBAS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AGP\Desktop\APOYO-MAT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBC495B7-B220-4A31-9E62-A341D805FE98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96D249E7-9146-4CF8-BE7C-F5AAE53B631C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{051C6437-CF6D-435E-ACB8-F6B20B0C248C}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="75">
   <si>
     <t>CODIGO</t>
   </si>
@@ -60,36 +60,24 @@
     <t>SISTEMA BINARIO</t>
   </si>
   <si>
-    <t>211P - 2º ESO - NÚMEROS NATURALES - SISTEMA BINARIO</t>
-  </si>
-  <si>
     <t>212P</t>
   </si>
   <si>
     <t>SISTEMA SEXAGESIMAL</t>
   </si>
   <si>
-    <t>212P - 2º ESO - NÚMEROS NATURALES - SISTEMA SEXAGESIMAL</t>
-  </si>
-  <si>
     <t>213P</t>
   </si>
   <si>
     <t>OPERACIONES COMBINADAS CON NÚMEROS NATURALES</t>
   </si>
   <si>
-    <t>213P - 2º ESO - NÚMEROS NATURALES - OPERACIONES COMBINADAS CON NÚMEROS NATURALES</t>
-  </si>
-  <si>
     <t>219P</t>
   </si>
   <si>
     <t>GLOBAL NÚMEROS NATURALES SIN DIVISIBILIDAD</t>
   </si>
   <si>
-    <t>219P - 2º ESO - NÚMEROS NATURALES - GLOBAL NÚMEROS NATURALES SIN DIVISIBILIDAD</t>
-  </si>
-  <si>
     <t>221P</t>
   </si>
   <si>
@@ -99,117 +87,78 @@
     <t>MÚLTIPLOS Y DIVISORES: RECONOCIMIENTO</t>
   </si>
   <si>
-    <t>221P - 2º ESO - DIVISIBILIDAD - MÚLTIPLOS Y DIVISORES: RECONOCIMIENTO</t>
-  </si>
-  <si>
     <t>222P</t>
   </si>
   <si>
     <t>MÚLTIPLOS DE UN NÚMERO</t>
   </si>
   <si>
-    <t>222P - 2º ESO - DIVISIBILIDAD - MÚLTIPLOS DE UN NÚMERO</t>
-  </si>
-  <si>
     <t>223P</t>
   </si>
   <si>
     <t>DIVISORES DE UN NÚMERO</t>
   </si>
   <si>
-    <t>223P - 2º ESO - DIVISIBILIDAD - DIVISORES DE UN NÚMERO</t>
-  </si>
-  <si>
     <t>224P</t>
   </si>
   <si>
     <t>CRITERIOS DE DIVISIBILIDAD</t>
   </si>
   <si>
-    <t>224P - 2º ESO - DIVISIBILIDAD - CRITERIOS DE DIVISIBILIDAD</t>
-  </si>
-  <si>
     <t>225P</t>
   </si>
   <si>
     <t>DESCOMPOSICIÓN EN FACTORES PRIMOS</t>
   </si>
   <si>
-    <t>225P - 2º ESO - DIVISIBILIDAD - DESCOMPOSICIÓN EN FACTORES PRIMOS</t>
-  </si>
-  <si>
     <t>226P</t>
   </si>
   <si>
     <t>CÁLCULO DEL M.C.M. Y M.C.D.</t>
   </si>
   <si>
-    <t>226P - 2º ESO - DIVISIBILIDAD - CÁLCULO DEL M.C.M. Y M.C.D.</t>
-  </si>
-  <si>
     <t>227P</t>
   </si>
   <si>
     <t>PROBLEMAS DE M.C.D. Y M.C.M.</t>
   </si>
   <si>
-    <t>227P - 2º ESO - DIVISIBILIDAD - PROBLEMAS DE M.C.D. Y M.C.M.</t>
-  </si>
-  <si>
     <t>229P</t>
   </si>
   <si>
     <t>GLOBAL DIVISIBILIDAD</t>
   </si>
   <si>
-    <t>229P - 2º ESO - DIVISIBILIDAD - GLOBAL DIVISIBILIDAD</t>
-  </si>
-  <si>
     <t>231P</t>
   </si>
   <si>
     <t>NÚMEROS ENTEROS</t>
   </si>
   <si>
-    <t>231P - 2º ESO - NÚMEROS ENTEROS - NÚMEROS ENTEROS</t>
-  </si>
-  <si>
     <t>232P</t>
   </si>
   <si>
     <t>OPERACIONES CON NÚMEROS ENTEROS</t>
   </si>
   <si>
-    <t>232P - 2º ESO - NÚMEROS ENTEROS - OPERACIONES CON NÚMEROS ENTEROS</t>
-  </si>
-  <si>
     <t>233P</t>
   </si>
   <si>
     <t>POTENCIAS Y RAÍCES CON NÚMEROS ENTEROS</t>
   </si>
   <si>
-    <t>233P - 2º ESO - NÚMEROS ENTEROS - POTENCIAS Y RAÍCES CON NÚMEROS ENTEROS</t>
-  </si>
-  <si>
     <t>234P</t>
   </si>
   <si>
     <t>PROBLEMAS CON NÚMEROS ENTEROS</t>
   </si>
   <si>
-    <t>234P - 2º ESO - NÚMEROS ENTEROS - PROBLEMAS CON NÚMEROS ENTEROS</t>
-  </si>
-  <si>
     <t>239P</t>
   </si>
   <si>
     <t>GLOBAL NÚMEROS ENTEROS</t>
   </si>
   <si>
-    <t>239P - 2º ESO - NÚMEROS ENTEROS - GLOBAL NÚMEROS ENTEROS</t>
-  </si>
-  <si>
     <t>241P</t>
   </si>
   <si>
@@ -219,54 +168,36 @@
     <t>ÓRDENES Y UNIDADES DECIMALES</t>
   </si>
   <si>
-    <t>241P - 2º ESO - NÚMEROS DECIMALES - ÓRDENES Y UNIDADES DECIMALES</t>
-  </si>
-  <si>
     <t>242P</t>
   </si>
   <si>
     <t>REPRESENTACIÓN Y ORDENACIÓN DE NÚMEROS DECIMALES</t>
   </si>
   <si>
-    <t>242P - 2º ESO - NÚMEROS DECIMALES - REPRESENTACIÓN Y ORDENACIÓN DE NÚMEROS DECIMALES</t>
-  </si>
-  <si>
     <t>243P</t>
   </si>
   <si>
     <t>OPERACIONES CON NÚMEROS DECIMALES</t>
   </si>
   <si>
-    <t>243P - 2º ESO - NÚMEROS DECIMALES - OPERACIONES CON NÚMEROS DECIMALES</t>
-  </si>
-  <si>
     <t>244P</t>
   </si>
   <si>
     <t>RAÍZ CUADRADA CON NÚMEROS DECIMALES</t>
   </si>
   <si>
-    <t>244P - 2º ESO - NÚMEROS DECIMALES - RAÍZ CUADRADA CON NÚMEROS DECIMALES</t>
-  </si>
-  <si>
     <t>245P</t>
   </si>
   <si>
     <t>RESOLUCIÓN DE PROBLEMAS CON NÚMEROS DECIMALES</t>
   </si>
   <si>
-    <t>245P - 2º ESO - NÚMEROS DECIMALES - RESOLUCIÓN DE PROBLEMAS CON NÚMEROS DECIMALES</t>
-  </si>
-  <si>
     <t>249P</t>
   </si>
   <si>
     <t>GLOBAL NÚMEROS DECIMALES</t>
   </si>
   <si>
-    <t>249P - 2º ESO - NÚMEROS DECIMALES - GLOBAL NÚMEROS DECIMALES</t>
-  </si>
-  <si>
     <t>251P</t>
   </si>
   <si>
@@ -276,36 +207,24 @@
     <t>CONCEPTO, REPRESENTACIÓN VISUAL Y RECTA NUMÉRICA</t>
   </si>
   <si>
-    <t>251P - 2º ESO - FRACCIONES - CONCEPTO, REPRESENTACIÓN VISUAL Y RECTA NUMÉRICA</t>
-  </si>
-  <si>
     <t>252P</t>
   </si>
   <si>
     <t>EQUIVALENCIA, SIMPLIFICACIÓN Y NÚMEROS RACIONALES</t>
   </si>
   <si>
-    <t>252P - 2º ESO - FRACCIONES - EQUIVALENCIA, SIMPLIFICACIÓN Y NÚMEROS RACIONALES</t>
-  </si>
-  <si>
     <t>253P</t>
   </si>
   <si>
     <t>OPERACIONES CON FRACCIONES</t>
   </si>
   <si>
-    <t>253P - 2º ESO - FRACCIONES - OPERACIONES CON FRACCIONES</t>
-  </si>
-  <si>
     <t>254P</t>
   </si>
   <si>
     <t>RESOLUCIÓN DE PROBLEMAS CON FRACCIONES</t>
   </si>
   <si>
-    <t>254P - 2º ESO - FRACCIONES - RESOLUCIÓN DE PROBLEMAS CON FRACCIONES</t>
-  </si>
-  <si>
     <t>MATERIAL</t>
   </si>
   <si>
@@ -325,6 +244,15 @@
   </si>
   <si>
     <t>FICHA</t>
+  </si>
+  <si>
+    <t>6º PRIMARIA</t>
+  </si>
+  <si>
+    <t>4º PRIMARIA</t>
+  </si>
+  <si>
+    <t>5º PRIMARIA</t>
   </si>
 </sst>
 </file>
@@ -728,7 +656,7 @@
   <sheetData>
     <row r="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
-        <v>92</v>
+        <v>65</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>0</v>
@@ -751,7 +679,7 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
-        <v>93</v>
+        <v>66</v>
       </c>
       <c r="B2" s="4" t="s">
         <v>6</v>
@@ -765,17 +693,18 @@
       <c r="E2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="3" t="s">
-        <v>10</v>
+      <c r="F2" s="3" t="str">
+        <f>CONCATENATE(B2," - ",C2," - ",D2," - ",E2)</f>
+        <v>211P - 2º ESO - NÚMEROS NATURALES - SISTEMA BINARIO</v>
       </c>
       <c r="G2" s="4"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
-        <v>93</v>
+        <v>66</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>7</v>
@@ -784,19 +713,20 @@
         <v>8</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>13</v>
+        <v>11</v>
+      </c>
+      <c r="F3" s="3" t="str">
+        <f t="shared" ref="F3:F31" si="0">CONCATENATE(B3," - ",C3," - ",D3," - ",E3)</f>
+        <v>212P - 2º ESO - NÚMEROS NATURALES - SISTEMA SEXAGESIMAL</v>
       </c>
       <c r="G3" s="4"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
-        <v>93</v>
+        <v>66</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>7</v>
@@ -805,19 +735,20 @@
         <v>8</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>16</v>
+        <v>13</v>
+      </c>
+      <c r="F4" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>213P - 2º ESO - NÚMEROS NATURALES - OPERACIONES COMBINADAS CON NÚMEROS NATURALES</v>
       </c>
       <c r="G4" s="4"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
-        <v>93</v>
+        <v>66</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>7</v>
@@ -826,178 +757,187 @@
         <v>8</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>19</v>
+        <v>15</v>
+      </c>
+      <c r="F5" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>219P - 2º ESO - NÚMEROS NATURALES - GLOBAL NÚMEROS NATURALES SIN DIVISIBILIDAD</v>
       </c>
       <c r="G5" s="4"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
-        <v>93</v>
+        <v>66</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C6" s="4" t="s">
         <v>7</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>23</v>
+        <v>18</v>
+      </c>
+      <c r="F6" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>221P - 2º ESO - DIVISIBILIDAD - MÚLTIPLOS Y DIVISORES: RECONOCIMIENTO</v>
       </c>
       <c r="G6" s="4"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
-        <v>93</v>
+        <v>66</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="C7" s="4" t="s">
         <v>7</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>26</v>
+        <v>20</v>
+      </c>
+      <c r="F7" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>222P - 2º ESO - DIVISIBILIDAD - MÚLTIPLOS DE UN NÚMERO</v>
       </c>
       <c r="G7" s="4"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
-        <v>93</v>
+        <v>66</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="C8" s="4" t="s">
         <v>7</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>29</v>
+        <v>22</v>
+      </c>
+      <c r="F8" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>223P - 2º ESO - DIVISIBILIDAD - DIVISORES DE UN NÚMERO</v>
       </c>
       <c r="G8" s="4"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
-        <v>93</v>
+        <v>66</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="C9" s="4" t="s">
         <v>7</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>32</v>
+        <v>24</v>
+      </c>
+      <c r="F9" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>224P - 2º ESO - DIVISIBILIDAD - CRITERIOS DE DIVISIBILIDAD</v>
       </c>
       <c r="G9" s="4"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
-        <v>93</v>
+        <v>66</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="C10" s="4" t="s">
         <v>7</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>35</v>
+        <v>26</v>
+      </c>
+      <c r="F10" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>225P - 2º ESO - DIVISIBILIDAD - DESCOMPOSICIÓN EN FACTORES PRIMOS</v>
       </c>
       <c r="G10" s="4"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
-        <v>93</v>
+        <v>66</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="C11" s="4" t="s">
         <v>7</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>38</v>
+        <v>28</v>
+      </c>
+      <c r="F11" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>226P - 2º ESO - DIVISIBILIDAD - CÁLCULO DEL M.C.M. Y M.C.D.</v>
       </c>
       <c r="G11" s="4"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
-        <v>93</v>
+        <v>66</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="C12" s="4" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>41</v>
+        <v>30</v>
+      </c>
+      <c r="F12" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>227P - 2º ESO - DIVISIBILIDAD - PROBLEMAS DE M.C.D. Y M.C.M.</v>
       </c>
       <c r="G12" s="4"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
-        <v>93</v>
+        <v>66</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="C13" s="4" t="s">
         <v>7</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="F13" s="3" t="s">
-        <v>44</v>
+        <v>32</v>
+      </c>
+      <c r="F13" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>229P - 2º ESO - DIVISIBILIDAD - GLOBAL DIVISIBILIDAD</v>
       </c>
       <c r="G13" s="4">
         <v>20</v>
@@ -1005,106 +945,111 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="4" t="s">
-        <v>93</v>
+        <v>66</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="C14" s="4" t="s">
         <v>7</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>47</v>
+        <v>34</v>
+      </c>
+      <c r="F14" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>231P - 2º ESO - NÚMEROS ENTEROS - NÚMEROS ENTEROS</v>
       </c>
       <c r="G14" s="4"/>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="4" t="s">
-        <v>93</v>
+        <v>66</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="C15" s="4" t="s">
         <v>7</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="F15" s="3" t="s">
-        <v>50</v>
+        <v>36</v>
+      </c>
+      <c r="F15" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>232P - 2º ESO - NÚMEROS ENTEROS - OPERACIONES CON NÚMEROS ENTEROS</v>
       </c>
       <c r="G15" s="4"/>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="4" t="s">
-        <v>93</v>
+        <v>66</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>51</v>
+        <v>37</v>
       </c>
       <c r="C16" s="4" t="s">
         <v>7</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="F16" s="3" t="s">
-        <v>53</v>
+        <v>38</v>
+      </c>
+      <c r="F16" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>233P - 2º ESO - NÚMEROS ENTEROS - POTENCIAS Y RAÍCES CON NÚMEROS ENTEROS</v>
       </c>
       <c r="G16" s="4"/>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="4" t="s">
-        <v>93</v>
+        <v>66</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>54</v>
+        <v>39</v>
       </c>
       <c r="C17" s="4" t="s">
         <v>7</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="F17" s="3" t="s">
-        <v>56</v>
+        <v>40</v>
+      </c>
+      <c r="F17" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>234P - 2º ESO - NÚMEROS ENTEROS - PROBLEMAS CON NÚMEROS ENTEROS</v>
       </c>
       <c r="G17" s="4"/>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" s="4" t="s">
-        <v>93</v>
+        <v>66</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>57</v>
+        <v>41</v>
       </c>
       <c r="C18" s="4" t="s">
         <v>7</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="F18" s="3" t="s">
-        <v>59</v>
+        <v>42</v>
+      </c>
+      <c r="F18" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>239P - 2º ESO - NÚMEROS ENTEROS - GLOBAL NÚMEROS ENTEROS</v>
       </c>
       <c r="G18" s="4">
         <v>19</v>
@@ -1112,148 +1057,155 @@
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" s="4" t="s">
-        <v>93</v>
+        <v>66</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>60</v>
+        <v>43</v>
       </c>
       <c r="C19" s="4" t="s">
         <v>7</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>61</v>
+        <v>44</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="F19" s="3" t="s">
-        <v>63</v>
+        <v>45</v>
+      </c>
+      <c r="F19" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>241P - 2º ESO - NÚMEROS DECIMALES - ÓRDENES Y UNIDADES DECIMALES</v>
       </c>
       <c r="G19" s="4"/>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" s="4" t="s">
-        <v>93</v>
+        <v>66</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>64</v>
+        <v>46</v>
       </c>
       <c r="C20" s="4" t="s">
         <v>7</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>61</v>
+        <v>44</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="F20" s="3" t="s">
-        <v>66</v>
+        <v>47</v>
+      </c>
+      <c r="F20" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>242P - 2º ESO - NÚMEROS DECIMALES - REPRESENTACIÓN Y ORDENACIÓN DE NÚMEROS DECIMALES</v>
       </c>
       <c r="G20" s="4"/>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" s="4" t="s">
-        <v>93</v>
+        <v>66</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>67</v>
+        <v>48</v>
       </c>
       <c r="C21" s="4" t="s">
         <v>7</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>61</v>
+        <v>44</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>69</v>
+        <v>49</v>
+      </c>
+      <c r="F21" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>243P - 2º ESO - NÚMEROS DECIMALES - OPERACIONES CON NÚMEROS DECIMALES</v>
       </c>
       <c r="G21" s="4"/>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" s="4" t="s">
-        <v>93</v>
+        <v>66</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="C22" s="4" t="s">
         <v>7</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>61</v>
+        <v>44</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="F22" s="3" t="s">
-        <v>72</v>
+        <v>51</v>
+      </c>
+      <c r="F22" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>244P - 2º ESO - NÚMEROS DECIMALES - RAÍZ CUADRADA CON NÚMEROS DECIMALES</v>
       </c>
       <c r="G22" s="4"/>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" s="4" t="s">
-        <v>93</v>
+        <v>66</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>73</v>
+        <v>52</v>
       </c>
       <c r="C23" s="4" t="s">
         <v>7</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>61</v>
+        <v>44</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="F23" s="3" t="s">
-        <v>75</v>
+        <v>53</v>
+      </c>
+      <c r="F23" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>245P - 2º ESO - NÚMEROS DECIMALES - RESOLUCIÓN DE PROBLEMAS CON NÚMEROS DECIMALES</v>
       </c>
       <c r="G23" s="4"/>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" s="4" t="s">
-        <v>93</v>
+        <v>66</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>76</v>
+        <v>54</v>
       </c>
       <c r="C24" s="4" t="s">
         <v>7</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>61</v>
+        <v>44</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="F24" s="3" t="s">
-        <v>78</v>
+        <v>55</v>
+      </c>
+      <c r="F24" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>249P - 2º ESO - NÚMEROS DECIMALES - GLOBAL NÚMEROS DECIMALES</v>
       </c>
       <c r="G24" s="4"/>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" s="4" t="s">
-        <v>93</v>
+        <v>66</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>79</v>
+        <v>56</v>
       </c>
       <c r="C25" s="4" t="s">
         <v>7</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>80</v>
+        <v>57</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="F25" s="3" t="s">
-        <v>82</v>
+        <v>58</v>
+      </c>
+      <c r="F25" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>251P - 2º ESO - FRACCIONES - CONCEPTO, REPRESENTACIÓN VISUAL Y RECTA NUMÉRICA</v>
       </c>
       <c r="G25" s="4">
         <v>15</v>
@@ -1261,22 +1213,23 @@
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" s="4" t="s">
-        <v>93</v>
+        <v>66</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>83</v>
+        <v>59</v>
       </c>
       <c r="C26" s="4" t="s">
         <v>7</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>80</v>
+        <v>57</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="F26" s="3" t="s">
-        <v>85</v>
+        <v>60</v>
+      </c>
+      <c r="F26" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>252P - 2º ESO - FRACCIONES - EQUIVALENCIA, SIMPLIFICACIÓN Y NÚMEROS RACIONALES</v>
       </c>
       <c r="G26" s="4">
         <v>15</v>
@@ -1284,22 +1237,23 @@
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" s="4" t="s">
-        <v>93</v>
+        <v>66</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>86</v>
+        <v>61</v>
       </c>
       <c r="C27" s="4" t="s">
         <v>7</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>80</v>
+        <v>57</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="F27" s="3" t="s">
-        <v>88</v>
+        <v>62</v>
+      </c>
+      <c r="F27" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>253P - 2º ESO - FRACCIONES - OPERACIONES CON FRACCIONES</v>
       </c>
       <c r="G27" s="4">
         <v>14</v>
@@ -1307,22 +1261,23 @@
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" s="4" t="s">
-        <v>93</v>
+        <v>66</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>89</v>
+        <v>63</v>
       </c>
       <c r="C28" s="4" t="s">
         <v>7</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>80</v>
+        <v>57</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="F28" s="3" t="s">
-        <v>91</v>
+        <v>64</v>
+      </c>
+      <c r="F28" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>254P - 2º ESO - FRACCIONES - RESOLUCIÓN DE PROBLEMAS CON FRACCIONES</v>
       </c>
       <c r="G28" s="4">
         <v>20</v>
@@ -1330,22 +1285,23 @@
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" s="4" t="s">
-        <v>93</v>
+        <v>66</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>94</v>
+        <v>67</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>7</v>
+        <v>72</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>80</v>
+        <v>57</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>91</v>
+        <v>64</v>
+      </c>
+      <c r="F29" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>0654P - 6º PRIMARIA - FRACCIONES - RESOLUCIÓN DE PROBLEMAS CON FRACCIONES</v>
       </c>
       <c r="G29" s="4">
         <v>20</v>
@@ -1353,22 +1309,23 @@
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" s="4" t="s">
-        <v>98</v>
+        <v>71</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>95</v>
+        <v>68</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>7</v>
+        <v>74</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>80</v>
+        <v>57</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="F30" s="3" t="s">
-        <v>91</v>
+        <v>64</v>
+      </c>
+      <c r="F30" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>0531F - 5º PRIMARIA - FRACCIONES - RESOLUCIÓN DE PROBLEMAS CON FRACCIONES</v>
       </c>
       <c r="G30" s="4">
         <v>20</v>
@@ -1376,22 +1333,23 @@
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" s="4" t="s">
-        <v>97</v>
+        <v>70</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>96</v>
+        <v>69</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>7</v>
+        <v>73</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>80</v>
+        <v>57</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="F31" s="3" t="s">
-        <v>91</v>
+        <v>64</v>
+      </c>
+      <c r="F31" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>0416E - 4º PRIMARIA - FRACCIONES - RESOLUCIÓN DE PROBLEMAS CON FRACCIONES</v>
       </c>
       <c r="G31" s="4">
         <v>20</v>

--- a/APOYO_MAT_LISTADO_FICHAS_PRUEBAS.xlsx
+++ b/APOYO_MAT_LISTADO_FICHAS_PRUEBAS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AGP\Desktop\APOYO-MAT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96D249E7-9146-4CF8-BE7C-F5AAE53B631C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D25751A1-7B51-4551-806E-F0F0BC977268}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{051C6437-CF6D-435E-ACB8-F6B20B0C248C}"/>
   </bookViews>

--- a/APOYO_MAT_LISTADO_FICHAS_PRUEBAS.xlsx
+++ b/APOYO_MAT_LISTADO_FICHAS_PRUEBAS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AGP\Desktop\APOYO-MAT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D25751A1-7B51-4551-806E-F0F0BC977268}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EE4FB5F-715C-4647-B998-2E83C4FB9E00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{051C6437-CF6D-435E-ACB8-F6B20B0C248C}"/>
+    <workbookView xWindow="2664" yWindow="3360" windowWidth="17280" windowHeight="8880" xr2:uid="{051C6437-CF6D-435E-ACB8-F6B20B0C248C}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="71">
   <si>
     <t>CODIGO</t>
   </si>
@@ -84,21 +84,12 @@
     <t>DIVISIBILIDAD</t>
   </si>
   <si>
-    <t>MÚLTIPLOS Y DIVISORES: RECONOCIMIENTO</t>
-  </si>
-  <si>
     <t>222P</t>
   </si>
   <si>
-    <t>MÚLTIPLOS DE UN NÚMERO</t>
-  </si>
-  <si>
     <t>223P</t>
   </si>
   <si>
-    <t>DIVISORES DE UN NÚMERO</t>
-  </si>
-  <si>
     <t>224P</t>
   </si>
   <si>
@@ -111,15 +102,9 @@
     <t>DESCOMPOSICIÓN EN FACTORES PRIMOS</t>
   </si>
   <si>
-    <t>226P</t>
-  </si>
-  <si>
     <t>CÁLCULO DEL M.C.M. Y M.C.D.</t>
   </si>
   <si>
-    <t>227P</t>
-  </si>
-  <si>
     <t>PROBLEMAS DE M.C.D. Y M.C.M.</t>
   </si>
   <si>
@@ -253,6 +238,9 @@
   </si>
   <si>
     <t>5º PRIMARIA</t>
+  </si>
+  <si>
+    <t>MÚLTIPLOS Y DIVISORES</t>
   </si>
 </sst>
 </file>
@@ -642,7 +630,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE4216F7-0C51-4F64-B136-9F38940C606F}">
-  <dimension ref="A1:G31"/>
+  <dimension ref="A1:G29"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.44140625" style="1" bestFit="1" customWidth="1"/>
@@ -656,7 +644,7 @@
   <sheetData>
     <row r="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>0</v>
@@ -679,7 +667,7 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="B2" s="4" t="s">
         <v>6</v>
@@ -697,11 +685,13 @@
         <f>CONCATENATE(B2," - ",C2," - ",D2," - ",E2)</f>
         <v>211P - 2º ESO - NÚMEROS NATURALES - SISTEMA BINARIO</v>
       </c>
-      <c r="G2" s="4"/>
+      <c r="G2" s="4">
+        <v>5</v>
+      </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>10</v>
@@ -716,14 +706,16 @@
         <v>11</v>
       </c>
       <c r="F3" s="3" t="str">
-        <f t="shared" ref="F3:F31" si="0">CONCATENATE(B3," - ",C3," - ",D3," - ",E3)</f>
+        <f t="shared" ref="F3:F29" si="0">CONCATENATE(B3," - ",C3," - ",D3," - ",E3)</f>
         <v>212P - 2º ESO - NÚMEROS NATURALES - SISTEMA SEXAGESIMAL</v>
       </c>
-      <c r="G3" s="4"/>
+      <c r="G3" s="4">
+        <v>5</v>
+      </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>12</v>
@@ -741,11 +733,13 @@
         <f t="shared" si="0"/>
         <v>213P - 2º ESO - NÚMEROS NATURALES - OPERACIONES COMBINADAS CON NÚMEROS NATURALES</v>
       </c>
-      <c r="G4" s="4"/>
+      <c r="G4" s="4">
+        <v>5</v>
+      </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="B5" s="4" t="s">
         <v>14</v>
@@ -763,11 +757,13 @@
         <f t="shared" si="0"/>
         <v>219P - 2º ESO - NÚMEROS NATURALES - GLOBAL NÚMEROS NATURALES SIN DIVISIBILIDAD</v>
       </c>
-      <c r="G5" s="4"/>
+      <c r="G5" s="4">
+        <v>5</v>
+      </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="B6" s="4" t="s">
         <v>16</v>
@@ -779,20 +775,22 @@
         <v>17</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>18</v>
+        <v>70</v>
       </c>
       <c r="F6" s="3" t="str">
         <f t="shared" si="0"/>
-        <v>221P - 2º ESO - DIVISIBILIDAD - MÚLTIPLOS Y DIVISORES: RECONOCIMIENTO</v>
-      </c>
-      <c r="G6" s="4"/>
+        <v>221P - 2º ESO - DIVISIBILIDAD - MÚLTIPLOS Y DIVISORES</v>
+      </c>
+      <c r="G6" s="4">
+        <v>15</v>
+      </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C7" s="4" t="s">
         <v>7</v>
@@ -801,20 +799,22 @@
         <v>17</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F7" s="3" t="str">
         <f t="shared" si="0"/>
-        <v>222P - 2º ESO - DIVISIBILIDAD - MÚLTIPLOS DE UN NÚMERO</v>
-      </c>
-      <c r="G7" s="4"/>
+        <v>222P - 2º ESO - DIVISIBILIDAD - CRITERIOS DE DIVISIBILIDAD</v>
+      </c>
+      <c r="G7" s="4">
+        <v>5</v>
+      </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C8" s="4" t="s">
         <v>7</v>
@@ -823,20 +823,22 @@
         <v>17</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F8" s="3" t="str">
         <f t="shared" si="0"/>
-        <v>223P - 2º ESO - DIVISIBILIDAD - DIVISORES DE UN NÚMERO</v>
-      </c>
-      <c r="G8" s="4"/>
+        <v>223P - 2º ESO - DIVISIBILIDAD - DESCOMPOSICIÓN EN FACTORES PRIMOS</v>
+      </c>
+      <c r="G8" s="4">
+        <v>5</v>
+      </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="C9" s="4" t="s">
         <v>7</v>
@@ -849,16 +851,18 @@
       </c>
       <c r="F9" s="3" t="str">
         <f t="shared" si="0"/>
-        <v>224P - 2º ESO - DIVISIBILIDAD - CRITERIOS DE DIVISIBILIDAD</v>
-      </c>
-      <c r="G9" s="4"/>
+        <v>224P - 2º ESO - DIVISIBILIDAD - CÁLCULO DEL M.C.M. Y M.C.D.</v>
+      </c>
+      <c r="G9" s="4">
+        <v>5</v>
+      </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C10" s="4" t="s">
         <v>7</v>
@@ -867,20 +871,22 @@
         <v>17</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F10" s="3" t="str">
         <f t="shared" si="0"/>
-        <v>225P - 2º ESO - DIVISIBILIDAD - DESCOMPOSICIÓN EN FACTORES PRIMOS</v>
-      </c>
-      <c r="G10" s="4"/>
+        <v>225P - 2º ESO - DIVISIBILIDAD - PROBLEMAS DE M.C.D. Y M.C.M.</v>
+      </c>
+      <c r="G10" s="4">
+        <v>10</v>
+      </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C11" s="4" t="s">
         <v>7</v>
@@ -889,151 +895,153 @@
         <v>17</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F11" s="3" t="str">
         <f t="shared" si="0"/>
-        <v>226P - 2º ESO - DIVISIBILIDAD - CÁLCULO DEL M.C.M. Y M.C.D.</v>
-      </c>
-      <c r="G11" s="4"/>
+        <v>229P - 2º ESO - DIVISIBILIDAD - GLOBAL DIVISIBILIDAD</v>
+      </c>
+      <c r="G11" s="4">
+        <v>20</v>
+      </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="B12" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D12" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="C12" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>17</v>
-      </c>
       <c r="E12" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F12" s="3" t="str">
         <f t="shared" si="0"/>
-        <v>227P - 2º ESO - DIVISIBILIDAD - PROBLEMAS DE M.C.D. Y M.C.M.</v>
+        <v>231P - 2º ESO - NÚMEROS ENTEROS - NÚMEROS ENTEROS</v>
       </c>
       <c r="G12" s="4"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="B13" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E13" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C13" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>32</v>
-      </c>
       <c r="F13" s="3" t="str">
         <f t="shared" si="0"/>
-        <v>229P - 2º ESO - DIVISIBILIDAD - GLOBAL DIVISIBILIDAD</v>
-      </c>
-      <c r="G13" s="4">
-        <v>20</v>
-      </c>
+        <v>232P - 2º ESO - NÚMEROS ENTEROS - OPERACIONES CON NÚMEROS ENTEROS</v>
+      </c>
+      <c r="G13" s="4"/>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="4" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="B14" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E14" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="C14" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>34</v>
-      </c>
       <c r="F14" s="3" t="str">
         <f t="shared" si="0"/>
-        <v>231P - 2º ESO - NÚMEROS ENTEROS - NÚMEROS ENTEROS</v>
+        <v>233P - 2º ESO - NÚMEROS ENTEROS - POTENCIAS Y RAÍCES CON NÚMEROS ENTEROS</v>
       </c>
       <c r="G14" s="4"/>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="4" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="B15" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E15" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C15" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>36</v>
-      </c>
       <c r="F15" s="3" t="str">
         <f t="shared" si="0"/>
-        <v>232P - 2º ESO - NÚMEROS ENTEROS - OPERACIONES CON NÚMEROS ENTEROS</v>
+        <v>234P - 2º ESO - NÚMEROS ENTEROS - PROBLEMAS CON NÚMEROS ENTEROS</v>
       </c>
       <c r="G15" s="4"/>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="4" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="B16" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E16" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="C16" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="E16" s="3" t="s">
-        <v>38</v>
-      </c>
       <c r="F16" s="3" t="str">
         <f t="shared" si="0"/>
-        <v>233P - 2º ESO - NÚMEROS ENTEROS - POTENCIAS Y RAÍCES CON NÚMEROS ENTEROS</v>
-      </c>
-      <c r="G16" s="4"/>
+        <v>239P - 2º ESO - NÚMEROS ENTEROS - GLOBAL NÚMEROS ENTEROS</v>
+      </c>
+      <c r="G16" s="4">
+        <v>19</v>
+      </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="4" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="B17" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D17" s="3" t="s">
         <v>39</v>
-      </c>
-      <c r="C17" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>34</v>
       </c>
       <c r="E17" s="3" t="s">
         <v>40</v>
       </c>
       <c r="F17" s="3" t="str">
         <f t="shared" si="0"/>
-        <v>234P - 2º ESO - NÚMEROS ENTEROS - PROBLEMAS CON NÚMEROS ENTEROS</v>
+        <v>241P - 2º ESO - NÚMEROS DECIMALES - ÓRDENES Y UNIDADES DECIMALES</v>
       </c>
       <c r="G17" s="4"/>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" s="4" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="B18" s="4" t="s">
         <v>41</v>
@@ -1042,22 +1050,20 @@
         <v>7</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="E18" s="3" t="s">
         <v>42</v>
       </c>
       <c r="F18" s="3" t="str">
         <f t="shared" si="0"/>
-        <v>239P - 2º ESO - NÚMEROS ENTEROS - GLOBAL NÚMEROS ENTEROS</v>
-      </c>
-      <c r="G18" s="4">
-        <v>19</v>
-      </c>
+        <v>242P - 2º ESO - NÚMEROS DECIMALES - REPRESENTACIÓN Y ORDENACIÓN DE NÚMEROS DECIMALES</v>
+      </c>
+      <c r="G18" s="4"/>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" s="4" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="B19" s="4" t="s">
         <v>43</v>
@@ -1066,108 +1072,110 @@
         <v>7</v>
       </c>
       <c r="D19" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="E19" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="E19" s="3" t="s">
-        <v>45</v>
-      </c>
       <c r="F19" s="3" t="str">
         <f t="shared" si="0"/>
-        <v>241P - 2º ESO - NÚMEROS DECIMALES - ÓRDENES Y UNIDADES DECIMALES</v>
+        <v>243P - 2º ESO - NÚMEROS DECIMALES - OPERACIONES CON NÚMEROS DECIMALES</v>
       </c>
       <c r="G19" s="4"/>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" s="4" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="B20" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="E20" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="C20" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>47</v>
-      </c>
       <c r="F20" s="3" t="str">
         <f t="shared" si="0"/>
-        <v>242P - 2º ESO - NÚMEROS DECIMALES - REPRESENTACIÓN Y ORDENACIÓN DE NÚMEROS DECIMALES</v>
+        <v>244P - 2º ESO - NÚMEROS DECIMALES - RAÍZ CUADRADA CON NÚMEROS DECIMALES</v>
       </c>
       <c r="G20" s="4"/>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" s="4" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="B21" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="E21" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="C21" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>49</v>
-      </c>
       <c r="F21" s="3" t="str">
         <f t="shared" si="0"/>
-        <v>243P - 2º ESO - NÚMEROS DECIMALES - OPERACIONES CON NÚMEROS DECIMALES</v>
+        <v>245P - 2º ESO - NÚMEROS DECIMALES - RESOLUCIÓN DE PROBLEMAS CON NÚMEROS DECIMALES</v>
       </c>
       <c r="G21" s="4"/>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" s="4" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="B22" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="E22" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="C22" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="D22" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>51</v>
-      </c>
       <c r="F22" s="3" t="str">
         <f t="shared" si="0"/>
-        <v>244P - 2º ESO - NÚMEROS DECIMALES - RAÍZ CUADRADA CON NÚMEROS DECIMALES</v>
+        <v>249P - 2º ESO - NÚMEROS DECIMALES - GLOBAL NÚMEROS DECIMALES</v>
       </c>
       <c r="G22" s="4"/>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" s="4" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="B23" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D23" s="3" t="s">
         <v>52</v>
-      </c>
-      <c r="C23" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="D23" s="3" t="s">
-        <v>44</v>
       </c>
       <c r="E23" s="3" t="s">
         <v>53</v>
       </c>
       <c r="F23" s="3" t="str">
         <f t="shared" si="0"/>
-        <v>245P - 2º ESO - NÚMEROS DECIMALES - RESOLUCIÓN DE PROBLEMAS CON NÚMEROS DECIMALES</v>
-      </c>
-      <c r="G23" s="4"/>
+        <v>251P - 2º ESO - FRACCIONES - CONCEPTO, REPRESENTACIÓN VISUAL Y RECTA NUMÉRICA</v>
+      </c>
+      <c r="G23" s="4">
+        <v>15</v>
+      </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" s="4" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="B24" s="4" t="s">
         <v>54</v>
@@ -1176,20 +1184,22 @@
         <v>7</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="E24" s="3" t="s">
         <v>55</v>
       </c>
       <c r="F24" s="3" t="str">
         <f t="shared" si="0"/>
-        <v>249P - 2º ESO - NÚMEROS DECIMALES - GLOBAL NÚMEROS DECIMALES</v>
-      </c>
-      <c r="G24" s="4"/>
+        <v>252P - 2º ESO - FRACCIONES - EQUIVALENCIA, SIMPLIFICACIÓN Y NÚMEROS RACIONALES</v>
+      </c>
+      <c r="G24" s="4">
+        <v>15</v>
+      </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" s="4" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="B25" s="4" t="s">
         <v>56</v>
@@ -1198,65 +1208,65 @@
         <v>7</v>
       </c>
       <c r="D25" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="E25" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="E25" s="3" t="s">
-        <v>58</v>
-      </c>
       <c r="F25" s="3" t="str">
         <f t="shared" si="0"/>
-        <v>251P - 2º ESO - FRACCIONES - CONCEPTO, REPRESENTACIÓN VISUAL Y RECTA NUMÉRICA</v>
+        <v>253P - 2º ESO - FRACCIONES - OPERACIONES CON FRACCIONES</v>
       </c>
       <c r="G25" s="4">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" s="4" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="B26" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="E26" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="C26" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="D26" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="E26" s="3" t="s">
-        <v>60</v>
-      </c>
       <c r="F26" s="3" t="str">
         <f t="shared" si="0"/>
-        <v>252P - 2º ESO - FRACCIONES - EQUIVALENCIA, SIMPLIFICACIÓN Y NÚMEROS RACIONALES</v>
+        <v>254P - 2º ESO - FRACCIONES - RESOLUCIÓN DE PROBLEMAS CON FRACCIONES</v>
       </c>
       <c r="G26" s="4">
-        <v>15</v>
+        <v>20</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" s="4" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>7</v>
+        <v>67</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="F27" s="3" t="str">
         <f t="shared" si="0"/>
-        <v>253P - 2º ESO - FRACCIONES - OPERACIONES CON FRACCIONES</v>
+        <v>0654P - 6º PRIMARIA - FRACCIONES - RESOLUCIÓN DE PROBLEMAS CON FRACCIONES</v>
       </c>
       <c r="G27" s="4">
-        <v>14</v>
+        <v>20</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.3">
@@ -1267,17 +1277,17 @@
         <v>63</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>7</v>
+        <v>69</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="F28" s="3" t="str">
         <f t="shared" si="0"/>
-        <v>254P - 2º ESO - FRACCIONES - RESOLUCIÓN DE PROBLEMAS CON FRACCIONES</v>
+        <v>0531F - 5º PRIMARIA - FRACCIONES - RESOLUCIÓN DE PROBLEMAS CON FRACCIONES</v>
       </c>
       <c r="G28" s="4">
         <v>20</v>
@@ -1285,73 +1295,25 @@
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" s="4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="F29" s="3" t="str">
         <f t="shared" si="0"/>
-        <v>0654P - 6º PRIMARIA - FRACCIONES - RESOLUCIÓN DE PROBLEMAS CON FRACCIONES</v>
+        <v>0416E - 4º PRIMARIA - FRACCIONES - RESOLUCIÓN DE PROBLEMAS CON FRACCIONES</v>
       </c>
       <c r="G29" s="4">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A30" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="B30" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="C30" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="D30" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="E30" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="F30" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v>0531F - 5º PRIMARIA - FRACCIONES - RESOLUCIÓN DE PROBLEMAS CON FRACCIONES</v>
-      </c>
-      <c r="G30" s="4">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A31" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="B31" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="C31" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="D31" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="E31" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="F31" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v>0416E - 4º PRIMARIA - FRACCIONES - RESOLUCIÓN DE PROBLEMAS CON FRACCIONES</v>
-      </c>
-      <c r="G31" s="4">
         <v>20</v>
       </c>
     </row>

--- a/APOYO_MAT_LISTADO_FICHAS_PRUEBAS.xlsx
+++ b/APOYO_MAT_LISTADO_FICHAS_PRUEBAS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AGP\Desktop\APOYO-MAT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EE4FB5F-715C-4647-B998-2E83C4FB9E00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F550A092-CB87-4B8E-8DAB-2DF17446A9CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2664" yWindow="3360" windowWidth="17280" windowHeight="8880" xr2:uid="{051C6437-CF6D-435E-ACB8-F6B20B0C248C}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{051C6437-CF6D-435E-ACB8-F6B20B0C248C}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="77">
   <si>
     <t>CODIGO</t>
   </si>
@@ -241,6 +241,24 @@
   </si>
   <si>
     <t>MÚLTIPLOS Y DIVISORES</t>
+  </si>
+  <si>
+    <t>re</t>
+  </si>
+  <si>
+    <t>ewq</t>
+  </si>
+  <si>
+    <t>asassdd</t>
+  </si>
+  <si>
+    <t>RRRE</t>
+  </si>
+  <si>
+    <t>TTTTTY</t>
+  </si>
+  <si>
+    <t>UUUUUUI</t>
   </si>
 </sst>
 </file>
@@ -925,7 +943,9 @@
         <f t="shared" si="0"/>
         <v>231P - 2º ESO - NÚMEROS ENTEROS - NÚMEROS ENTEROS</v>
       </c>
-      <c r="G12" s="4"/>
+      <c r="G12" s="4">
+        <v>15</v>
+      </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
@@ -947,7 +967,9 @@
         <f t="shared" si="0"/>
         <v>232P - 2º ESO - NÚMEROS ENTEROS - OPERACIONES CON NÚMEROS ENTEROS</v>
       </c>
-      <c r="G13" s="4"/>
+      <c r="G13" s="4">
+        <v>15</v>
+      </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="4" t="s">
@@ -969,7 +991,9 @@
         <f t="shared" si="0"/>
         <v>233P - 2º ESO - NÚMEROS ENTEROS - POTENCIAS Y RAÍCES CON NÚMEROS ENTEROS</v>
       </c>
-      <c r="G14" s="4"/>
+      <c r="G14" s="4">
+        <v>15</v>
+      </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="4" t="s">
@@ -991,7 +1015,9 @@
         <f t="shared" si="0"/>
         <v>234P - 2º ESO - NÚMEROS ENTEROS - PROBLEMAS CON NÚMEROS ENTEROS</v>
       </c>
-      <c r="G15" s="4"/>
+      <c r="G15" s="4">
+        <v>5</v>
+      </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="4" t="s">
@@ -1037,7 +1063,9 @@
         <f t="shared" si="0"/>
         <v>241P - 2º ESO - NÚMEROS DECIMALES - ÓRDENES Y UNIDADES DECIMALES</v>
       </c>
-      <c r="G17" s="4"/>
+      <c r="G17" s="4">
+        <v>15</v>
+      </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" s="4" t="s">
@@ -1059,7 +1087,9 @@
         <f t="shared" si="0"/>
         <v>242P - 2º ESO - NÚMEROS DECIMALES - REPRESENTACIÓN Y ORDENACIÓN DE NÚMEROS DECIMALES</v>
       </c>
-      <c r="G18" s="4"/>
+      <c r="G18" s="4">
+        <v>25</v>
+      </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" s="4" t="s">
@@ -1081,7 +1111,9 @@
         <f t="shared" si="0"/>
         <v>243P - 2º ESO - NÚMEROS DECIMALES - OPERACIONES CON NÚMEROS DECIMALES</v>
       </c>
-      <c r="G19" s="4"/>
+      <c r="G19" s="4">
+        <v>20</v>
+      </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" s="4" t="s">
@@ -1103,7 +1135,9 @@
         <f t="shared" si="0"/>
         <v>244P - 2º ESO - NÚMEROS DECIMALES - RAÍZ CUADRADA CON NÚMEROS DECIMALES</v>
       </c>
-      <c r="G20" s="4"/>
+      <c r="G20" s="4">
+        <v>15</v>
+      </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" s="4" t="s">
@@ -1125,7 +1159,9 @@
         <f t="shared" si="0"/>
         <v>245P - 2º ESO - NÚMEROS DECIMALES - RESOLUCIÓN DE PROBLEMAS CON NÚMEROS DECIMALES</v>
       </c>
-      <c r="G21" s="4"/>
+      <c r="G21" s="4">
+        <v>5</v>
+      </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" s="4" t="s">
@@ -1147,7 +1183,9 @@
         <f t="shared" si="0"/>
         <v>249P - 2º ESO - NÚMEROS DECIMALES - GLOBAL NÚMEROS DECIMALES</v>
       </c>
-      <c r="G22" s="4"/>
+      <c r="G22" s="4">
+        <v>20</v>
+      </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" s="4" t="s">
@@ -1218,7 +1256,7 @@
         <v>253P - 2º ESO - FRACCIONES - OPERACIONES CON FRACCIONES</v>
       </c>
       <c r="G25" s="4">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
@@ -1256,17 +1294,17 @@
         <v>67</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>52</v>
+        <v>76</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="F27" s="3" t="str">
         <f t="shared" si="0"/>
-        <v>0654P - 6º PRIMARIA - FRACCIONES - RESOLUCIÓN DE PROBLEMAS CON FRACCIONES</v>
+        <v>0654P - 6º PRIMARIA - UUUUUUI - re</v>
       </c>
       <c r="G27" s="4">
-        <v>20</v>
+        <v>6</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.3">
@@ -1280,17 +1318,17 @@
         <v>69</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>52</v>
+        <v>75</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>59</v>
+        <v>72</v>
       </c>
       <c r="F28" s="3" t="str">
         <f t="shared" si="0"/>
-        <v>0531F - 5º PRIMARIA - FRACCIONES - RESOLUCIÓN DE PROBLEMAS CON FRACCIONES</v>
+        <v>0531F - 5º PRIMARIA - TTTTTY - ewq</v>
       </c>
       <c r="G28" s="4">
-        <v>20</v>
+        <v>7</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.3">
@@ -1304,17 +1342,17 @@
         <v>68</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>52</v>
+        <v>74</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>59</v>
+        <v>73</v>
       </c>
       <c r="F29" s="3" t="str">
         <f t="shared" si="0"/>
-        <v>0416E - 4º PRIMARIA - FRACCIONES - RESOLUCIÓN DE PROBLEMAS CON FRACCIONES</v>
+        <v>0416E - 4º PRIMARIA - RRRE - asassdd</v>
       </c>
       <c r="G29" s="4">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/APOYO_MAT_LISTADO_FICHAS_PRUEBAS.xlsx
+++ b/APOYO_MAT_LISTADO_FICHAS_PRUEBAS.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AGP\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AGP\Desktop\APOYO-MAT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E6EE624-AFC8-4C9C-9A69-F074B10D2195}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC97EC79-BAD1-4C09-84B8-EEE0ABFDACEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja1!$A$1:$G$107</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja1!$A$1:$G$103</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="85">
   <si>
     <t>MATERIAL</t>
   </si>
@@ -96,9 +96,6 @@
     <t>GLOBAL NÚMEROS NATURALES SIN DIVISIBILIDAD</t>
   </si>
   <si>
-    <t>219F</t>
-  </si>
-  <si>
     <t>221P</t>
   </si>
   <si>
@@ -153,9 +150,6 @@
     <t>GLOBAL DIVISIBILIDAD</t>
   </si>
   <si>
-    <t>229F</t>
-  </si>
-  <si>
     <t>231P</t>
   </si>
   <si>
@@ -198,9 +192,6 @@
     <t>GLOBAL NÚMEROS ENTEROS</t>
   </si>
   <si>
-    <t>239F</t>
-  </si>
-  <si>
     <t>241P</t>
   </si>
   <si>
@@ -253,9 +244,6 @@
   </si>
   <si>
     <t>GLOBAL NÚMEROS DECIMALES</t>
-  </si>
-  <si>
-    <t>249F</t>
   </si>
   <si>
     <t>251P</t>
@@ -604,7 +592,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G107"/>
+  <dimension ref="A1:G103"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12" style="1" customWidth="1"/>
@@ -702,7 +690,7 @@
         <v>15</v>
       </c>
       <c r="F4" s="4" t="str">
-        <f t="shared" ref="F4:F27" si="0">CONCATENATE(B4," - ",C4," - ",D4," - ",E4)</f>
+        <f t="shared" ref="F4:F25" si="0">CONCATENATE(B4," - ",C4," - ",D4," - ",E4)</f>
         <v>212P - 2º ESO - NÚMEROS NATURALES - SISTEMA SEXAGESIMAL</v>
       </c>
       <c r="G4" s="3">
@@ -803,7 +791,7 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>22</v>
@@ -812,44 +800,44 @@
         <v>9</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F9" s="4" t="str">
         <f t="shared" si="0"/>
-        <v>219F - 2º ESO - NÚMEROS NATURALES - GLOBAL NÚMEROS NATURALES SIN DIVISIBILIDAD</v>
-      </c>
-      <c r="G9" s="3"/>
+        <v>221P - 2º ESO - DIVISIBILIDAD - MÚLTIPLOS Y DIVISORES</v>
+      </c>
+      <c r="G9" s="3">
+        <v>15</v>
+      </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="B10" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D10" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="C10" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D10" s="4" t="s">
+      <c r="E10" s="4" t="s">
         <v>24</v>
-      </c>
-      <c r="E10" s="4" t="s">
-        <v>25</v>
       </c>
       <c r="F10" s="4" t="str">
         <f t="shared" si="0"/>
-        <v>221P - 2º ESO - DIVISIBILIDAD - MÚLTIPLOS Y DIVISORES</v>
-      </c>
-      <c r="G10" s="3">
-        <v>15</v>
-      </c>
+        <v>221F - 2º ESO - DIVISIBILIDAD - MÚLTIPLOS Y DIVISORES</v>
+      </c>
+      <c r="G10" s="3"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>26</v>
@@ -858,44 +846,44 @@
         <v>9</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F11" s="4" t="str">
         <f t="shared" si="0"/>
-        <v>221F - 2º ESO - DIVISIBILIDAD - MÚLTIPLOS Y DIVISORES</v>
-      </c>
-      <c r="G11" s="3"/>
+        <v>222P - 2º ESO - DIVISIBILIDAD - CRITERIOS DE DIVISIBILIDAD</v>
+      </c>
+      <c r="G11" s="3">
+        <v>5</v>
+      </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="B12" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E12" s="4" t="s">
         <v>27</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D12" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="E12" s="4" t="s">
-        <v>28</v>
       </c>
       <c r="F12" s="4" t="str">
         <f t="shared" si="0"/>
-        <v>222P - 2º ESO - DIVISIBILIDAD - CRITERIOS DE DIVISIBILIDAD</v>
-      </c>
-      <c r="G12" s="3">
-        <v>5</v>
-      </c>
+        <v>222F - 2º ESO - DIVISIBILIDAD - CRITERIOS DE DIVISIBILIDAD</v>
+      </c>
+      <c r="G12" s="3"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>29</v>
@@ -904,44 +892,44 @@
         <v>9</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F13" s="4" t="str">
         <f t="shared" si="0"/>
-        <v>222F - 2º ESO - DIVISIBILIDAD - CRITERIOS DE DIVISIBILIDAD</v>
-      </c>
-      <c r="G13" s="3"/>
+        <v>223P - 2º ESO - DIVISIBILIDAD - DESCOMPOSICIÓN EN FACTORES PRIMOS</v>
+      </c>
+      <c r="G13" s="3">
+        <v>5</v>
+      </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="3" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="B14" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E14" s="4" t="s">
         <v>30</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D14" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="E14" s="4" t="s">
-        <v>31</v>
       </c>
       <c r="F14" s="4" t="str">
         <f t="shared" si="0"/>
-        <v>223P - 2º ESO - DIVISIBILIDAD - DESCOMPOSICIÓN EN FACTORES PRIMOS</v>
-      </c>
-      <c r="G14" s="3">
-        <v>5</v>
-      </c>
+        <v>223F - 2º ESO - DIVISIBILIDAD - DESCOMPOSICIÓN EN FACTORES PRIMOS</v>
+      </c>
+      <c r="G14" s="3"/>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>32</v>
@@ -950,44 +938,44 @@
         <v>9</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F15" s="4" t="str">
         <f t="shared" si="0"/>
-        <v>223F - 2º ESO - DIVISIBILIDAD - DESCOMPOSICIÓN EN FACTORES PRIMOS</v>
-      </c>
-      <c r="G15" s="3"/>
+        <v>224P - 2º ESO - DIVISIBILIDAD - CÁLCULO DEL M.C.M. Y M.C.D.</v>
+      </c>
+      <c r="G15" s="3">
+        <v>5</v>
+      </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="B16" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E16" s="4" t="s">
         <v>33</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D16" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="E16" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="F16" s="4" t="str">
         <f t="shared" si="0"/>
-        <v>224P - 2º ESO - DIVISIBILIDAD - CÁLCULO DEL M.C.M. Y M.C.D.</v>
-      </c>
-      <c r="G16" s="3">
-        <v>5</v>
-      </c>
+        <v>224F - 2º ESO - DIVISIBILIDAD - CÁLCULO DEL M.C.M. Y M.C.D.</v>
+      </c>
+      <c r="G16" s="3"/>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="3" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>35</v>
@@ -996,44 +984,44 @@
         <v>9</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F17" s="4" t="str">
         <f t="shared" si="0"/>
-        <v>224F - 2º ESO - DIVISIBILIDAD - CÁLCULO DEL M.C.M. Y M.C.D.</v>
-      </c>
-      <c r="G17" s="3"/>
+        <v>225P - 2º ESO - DIVISIBILIDAD - PROBLEMAS DE M.C.D. Y M.C.M.</v>
+      </c>
+      <c r="G17" s="3">
+        <v>10</v>
+      </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" s="3" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="B18" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E18" s="4" t="s">
         <v>36</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D18" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="E18" s="4" t="s">
-        <v>37</v>
       </c>
       <c r="F18" s="4" t="str">
         <f t="shared" si="0"/>
-        <v>225P - 2º ESO - DIVISIBILIDAD - PROBLEMAS DE M.C.D. Y M.C.M.</v>
-      </c>
-      <c r="G18" s="3">
-        <v>10</v>
-      </c>
+        <v>225F - 2º ESO - DIVISIBILIDAD - PROBLEMAS DE M.C.D. Y M.C.M.</v>
+      </c>
+      <c r="G18" s="3"/>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" s="3" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>38</v>
@@ -1042,39 +1030,41 @@
         <v>9</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F19" s="4" t="str">
         <f t="shared" si="0"/>
-        <v>225F - 2º ESO - DIVISIBILIDAD - PROBLEMAS DE M.C.D. Y M.C.M.</v>
-      </c>
-      <c r="G19" s="3"/>
+        <v>229P - 2º ESO - DIVISIBILIDAD - GLOBAL DIVISIBILIDAD</v>
+      </c>
+      <c r="G19" s="3">
+        <v>20</v>
+      </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" s="3" t="s">
         <v>7</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C20" s="3" t="s">
         <v>9</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F20" s="4" t="str">
         <f t="shared" si="0"/>
-        <v>229P - 2º ESO - DIVISIBILIDAD - GLOBAL DIVISIBILIDAD</v>
+        <v>231P - 2º ESO - NÚMEROS ENTEROS - NÚMEROS ENTEROS</v>
       </c>
       <c r="G20" s="3">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
@@ -1082,20 +1072,20 @@
         <v>12</v>
       </c>
       <c r="B21" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D21" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="C21" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D21" s="4" t="s">
-        <v>24</v>
-      </c>
       <c r="E21" s="4" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F21" s="4" t="str">
         <f t="shared" si="0"/>
-        <v>229F - 2º ESO - DIVISIBILIDAD - GLOBAL DIVISIBILIDAD</v>
+        <v>231F - 2º ESO - NÚMEROS ENTEROS - NÚMEROS ENTEROS</v>
       </c>
       <c r="G21" s="3"/>
     </row>
@@ -1104,20 +1094,20 @@
         <v>7</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C22" s="3" t="s">
         <v>9</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F22" s="4" t="str">
         <f t="shared" si="0"/>
-        <v>231P - 2º ESO - NÚMEROS ENTEROS - NÚMEROS ENTEROS</v>
+        <v>232P - 2º ESO - NÚMEROS ENTEROS - OPERACIONES CON NÚMEROS ENTEROS</v>
       </c>
       <c r="G22" s="3">
         <v>15</v>
@@ -1128,20 +1118,20 @@
         <v>12</v>
       </c>
       <c r="B23" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="E23" s="4" t="s">
         <v>44</v>
-      </c>
-      <c r="C23" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D23" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="E23" s="4" t="s">
-        <v>43</v>
       </c>
       <c r="F23" s="4" t="str">
         <f t="shared" si="0"/>
-        <v>231F - 2º ESO - NÚMEROS ENTEROS - NÚMEROS ENTEROS</v>
+        <v>232F - 2º ESO - NÚMEROS ENTEROS - OPERACIONES CON NÚMEROS ENTEROS</v>
       </c>
       <c r="G23" s="3"/>
     </row>
@@ -1150,20 +1140,20 @@
         <v>7</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C24" s="3" t="s">
         <v>9</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F24" s="4" t="str">
         <f t="shared" si="0"/>
-        <v>232P - 2º ESO - NÚMEROS ENTEROS - OPERACIONES CON NÚMEROS ENTEROS</v>
+        <v>233P - 2º ESO - NÚMEROS ENTEROS - POTENCIAS Y RAÍCES CON NÚMEROS ENTEROS</v>
       </c>
       <c r="G24" s="3">
         <v>15</v>
@@ -1174,20 +1164,20 @@
         <v>12</v>
       </c>
       <c r="B25" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D25" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="E25" s="4" t="s">
         <v>47</v>
-      </c>
-      <c r="C25" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D25" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="E25" s="4" t="s">
-        <v>46</v>
       </c>
       <c r="F25" s="4" t="str">
         <f t="shared" si="0"/>
-        <v>232F - 2º ESO - NÚMEROS ENTEROS - OPERACIONES CON NÚMEROS ENTEROS</v>
+        <v>233F - 2º ESO - NÚMEROS ENTEROS - POTENCIAS Y RAÍCES CON NÚMEROS ENTEROS</v>
       </c>
       <c r="G25" s="3"/>
     </row>
@@ -1196,23 +1186,23 @@
         <v>7</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C26" s="3" t="s">
         <v>9</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F26" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>233P - 2º ESO - NÚMEROS ENTEROS - POTENCIAS Y RAÍCES CON NÚMEROS ENTEROS</v>
+        <f t="shared" ref="F26:F47" si="1">CONCATENATE(B26," - ",C26," - ",D26," - ",E26)</f>
+        <v>234P - 2º ESO - NÚMEROS ENTEROS - PROBLEMAS CON NÚMEROS ENTEROS</v>
       </c>
       <c r="G26" s="3">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.3">
@@ -1220,20 +1210,20 @@
         <v>12</v>
       </c>
       <c r="B27" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D27" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="E27" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="C27" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D27" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="E27" s="4" t="s">
-        <v>49</v>
-      </c>
       <c r="F27" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>233F - 2º ESO - NÚMEROS ENTEROS - POTENCIAS Y RAÍCES CON NÚMEROS ENTEROS</v>
+        <f t="shared" si="1"/>
+        <v>234F - 2º ESO - NÚMEROS ENTEROS - PROBLEMAS CON NÚMEROS ENTEROS</v>
       </c>
       <c r="G27" s="3"/>
     </row>
@@ -1242,299 +1232,301 @@
         <v>7</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C28" s="3" t="s">
         <v>9</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F28" s="4" t="str">
-        <f t="shared" ref="F28:F51" si="1">CONCATENATE(B28," - ",C28," - ",D28," - ",E28)</f>
-        <v>234P - 2º ESO - NÚMEROS ENTEROS - PROBLEMAS CON NÚMEROS ENTEROS</v>
+        <f t="shared" si="1"/>
+        <v>239P - 2º ESO - NÚMEROS ENTEROS - GLOBAL NÚMEROS ENTEROS</v>
       </c>
       <c r="G28" s="3">
-        <v>5</v>
+        <v>19</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" s="3" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C29" s="3" t="s">
         <v>9</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="F29" s="4" t="str">
         <f t="shared" si="1"/>
-        <v>234F - 2º ESO - NÚMEROS ENTEROS - PROBLEMAS CON NÚMEROS ENTEROS</v>
-      </c>
-      <c r="G29" s="3"/>
+        <v>241P - 2º ESO - NÚMEROS DECIMALES - ÓRDENES Y UNIDADES DECIMALES</v>
+      </c>
+      <c r="G29" s="3">
+        <v>15</v>
+      </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" s="3" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="C30" s="3" t="s">
         <v>9</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F30" s="4" t="str">
         <f t="shared" si="1"/>
-        <v>239P - 2º ESO - NÚMEROS ENTEROS - GLOBAL NÚMEROS ENTEROS</v>
-      </c>
-      <c r="G30" s="3">
-        <v>19</v>
-      </c>
+        <v>241F - 2º ESO - NÚMEROS DECIMALES - ÓRDENES Y UNIDADES DECIMALES</v>
+      </c>
+      <c r="G30" s="3"/>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" s="3" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C31" s="3" t="s">
         <v>9</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="F31" s="4" t="str">
         <f t="shared" si="1"/>
-        <v>239F - 2º ESO - NÚMEROS ENTEROS - GLOBAL NÚMEROS ENTEROS</v>
-      </c>
-      <c r="G31" s="3"/>
+        <v>242P - 2º ESO - NÚMEROS DECIMALES - REPRESENTACIÓN Y ORDENACIÓN DE NÚMEROS DECIMALES</v>
+      </c>
+      <c r="G31" s="3">
+        <v>25</v>
+      </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" s="3" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C32" s="3" t="s">
         <v>9</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="E32" s="4" t="s">
         <v>59</v>
       </c>
       <c r="F32" s="4" t="str">
         <f t="shared" si="1"/>
-        <v>241P - 2º ESO - NÚMEROS DECIMALES - ÓRDENES Y UNIDADES DECIMALES</v>
-      </c>
-      <c r="G32" s="3">
-        <v>15</v>
-      </c>
+        <v>242F - 2º ESO - NÚMEROS DECIMALES - REPRESENTACIÓN Y ORDENACIÓN DE NÚMEROS DECIMALES</v>
+      </c>
+      <c r="G32" s="3"/>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" s="3" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C33" s="3" t="s">
         <v>9</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F33" s="4" t="str">
         <f t="shared" si="1"/>
-        <v>241F - 2º ESO - NÚMEROS DECIMALES - ÓRDENES Y UNIDADES DECIMALES</v>
-      </c>
-      <c r="G33" s="3"/>
+        <v>243P - 2º ESO - NÚMEROS DECIMALES - OPERACIONES CON NÚMEROS DECIMALES</v>
+      </c>
+      <c r="G33" s="3">
+        <v>20</v>
+      </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34" s="3" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C34" s="3" t="s">
         <v>9</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="E34" s="4" t="s">
         <v>62</v>
       </c>
       <c r="F34" s="4" t="str">
         <f t="shared" si="1"/>
-        <v>242P - 2º ESO - NÚMEROS DECIMALES - REPRESENTACIÓN Y ORDENACIÓN DE NÚMEROS DECIMALES</v>
-      </c>
-      <c r="G34" s="3">
-        <v>25</v>
-      </c>
+        <v>243F - 2º ESO - NÚMEROS DECIMALES - OPERACIONES CON NÚMEROS DECIMALES</v>
+      </c>
+      <c r="G34" s="3"/>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35" s="3" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C35" s="3" t="s">
         <v>9</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="E35" s="4" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="F35" s="4" t="str">
         <f t="shared" si="1"/>
-        <v>242F - 2º ESO - NÚMEROS DECIMALES - REPRESENTACIÓN Y ORDENACIÓN DE NÚMEROS DECIMALES</v>
-      </c>
-      <c r="G35" s="3"/>
+        <v>244P - 2º ESO - NÚMEROS DECIMALES - RAÍZ CUADRADA CON NÚMEROS DECIMALES</v>
+      </c>
+      <c r="G35" s="3">
+        <v>15</v>
+      </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36" s="3" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C36" s="3" t="s">
         <v>9</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="E36" s="4" t="s">
         <v>65</v>
       </c>
       <c r="F36" s="4" t="str">
         <f t="shared" si="1"/>
-        <v>243P - 2º ESO - NÚMEROS DECIMALES - OPERACIONES CON NÚMEROS DECIMALES</v>
-      </c>
-      <c r="G36" s="3">
-        <v>20</v>
-      </c>
+        <v>244F - 2º ESO - NÚMEROS DECIMALES - RAÍZ CUADRADA CON NÚMEROS DECIMALES</v>
+      </c>
+      <c r="G36" s="3"/>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37" s="3" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C37" s="3" t="s">
         <v>9</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="E37" s="4" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="F37" s="4" t="str">
         <f t="shared" si="1"/>
-        <v>243F - 2º ESO - NÚMEROS DECIMALES - OPERACIONES CON NÚMEROS DECIMALES</v>
-      </c>
-      <c r="G37" s="3"/>
+        <v>245P - 2º ESO - NÚMEROS DECIMALES - RESOLUCIÓN DE PROBLEMAS CON NÚMEROS DECIMALES</v>
+      </c>
+      <c r="G37" s="3">
+        <v>5</v>
+      </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38" s="3" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C38" s="3" t="s">
         <v>9</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="E38" s="4" t="s">
         <v>68</v>
       </c>
       <c r="F38" s="4" t="str">
         <f t="shared" si="1"/>
-        <v>244P - 2º ESO - NÚMEROS DECIMALES - RAÍZ CUADRADA CON NÚMEROS DECIMALES</v>
-      </c>
-      <c r="G38" s="3">
-        <v>15</v>
-      </c>
+        <v>245F - 2º ESO - NÚMEROS DECIMALES - RESOLUCIÓN DE PROBLEMAS CON NÚMEROS DECIMALES</v>
+      </c>
+      <c r="G38" s="3"/>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39" s="3" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C39" s="3" t="s">
         <v>9</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="E39" s="4" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="F39" s="4" t="str">
         <f t="shared" si="1"/>
-        <v>244F - 2º ESO - NÚMEROS DECIMALES - RAÍZ CUADRADA CON NÚMEROS DECIMALES</v>
-      </c>
-      <c r="G39" s="3"/>
+        <v>249P - 2º ESO - NÚMEROS DECIMALES - GLOBAL NÚMEROS DECIMALES</v>
+      </c>
+      <c r="G39" s="3">
+        <v>20</v>
+      </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40" s="3" t="s">
         <v>7</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C40" s="3" t="s">
         <v>9</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>58</v>
+        <v>73</v>
       </c>
       <c r="E40" s="4" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="F40" s="4" t="str">
         <f t="shared" si="1"/>
-        <v>245P - 2º ESO - NÚMEROS DECIMALES - RESOLUCIÓN DE PROBLEMAS CON NÚMEROS DECIMALES</v>
+        <v>251P - 2º ESO - FRACCIONES - CONCEPTO, REPRESENTACIÓN VISUAL Y RECTA NUMÉRICA</v>
       </c>
       <c r="G40" s="3">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.3">
@@ -1542,20 +1534,20 @@
         <v>12</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="C41" s="3" t="s">
         <v>9</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>58</v>
+        <v>73</v>
       </c>
       <c r="E41" s="4" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="F41" s="4" t="str">
         <f t="shared" si="1"/>
-        <v>245F - 2º ESO - NÚMEROS DECIMALES - RESOLUCIÓN DE PROBLEMAS CON NÚMEROS DECIMALES</v>
+        <v>251F - 2º ESO - FRACCIONES - CONCEPTO, REPRESENTACIÓN VISUAL Y RECTA NUMÉRICA</v>
       </c>
       <c r="G41" s="3"/>
     </row>
@@ -1564,23 +1556,23 @@
         <v>7</v>
       </c>
       <c r="B42" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D42" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="C42" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D42" s="4" t="s">
-        <v>58</v>
-      </c>
       <c r="E42" s="4" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="F42" s="4" t="str">
         <f t="shared" si="1"/>
-        <v>249P - 2º ESO - NÚMEROS DECIMALES - GLOBAL NÚMEROS DECIMALES</v>
+        <v>252P - 2º ESO - FRACCIONES - EQUIVALENCIA, SIMPLIFICACIÓN Y NÚMEROS RACIONALES</v>
       </c>
       <c r="G42" s="3">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.3">
@@ -1588,20 +1580,20 @@
         <v>12</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="C43" s="3" t="s">
         <v>9</v>
       </c>
       <c r="D43" s="4" t="s">
-        <v>58</v>
+        <v>73</v>
       </c>
       <c r="E43" s="4" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="F43" s="4" t="str">
         <f t="shared" si="1"/>
-        <v>249F - 2º ESO - NÚMEROS DECIMALES - GLOBAL NÚMEROS DECIMALES</v>
+        <v>252F - 2º ESO - FRACCIONES - EQUIVALENCIA, SIMPLIFICACIÓN Y NÚMEROS RACIONALES</v>
       </c>
       <c r="G43" s="3"/>
     </row>
@@ -1610,20 +1602,20 @@
         <v>7</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="C44" s="3" t="s">
         <v>9</v>
       </c>
       <c r="D44" s="4" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="E44" s="4" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="F44" s="4" t="str">
         <f t="shared" si="1"/>
-        <v>251P - 2º ESO - FRACCIONES - CONCEPTO, REPRESENTACIÓN VISUAL Y RECTA NUMÉRICA</v>
+        <v>253P - 2º ESO - FRACCIONES - OPERACIONES CON FRACCIONES</v>
       </c>
       <c r="G44" s="3">
         <v>15</v>
@@ -1634,20 +1626,20 @@
         <v>12</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C45" s="3" t="s">
         <v>9</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="E45" s="4" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="F45" s="4" t="str">
         <f t="shared" si="1"/>
-        <v>251F - 2º ESO - FRACCIONES - CONCEPTO, REPRESENTACIÓN VISUAL Y RECTA NUMÉRICA</v>
+        <v>253F - 2º ESO - FRACCIONES - OPERACIONES CON FRACCIONES</v>
       </c>
       <c r="G45" s="3"/>
     </row>
@@ -1656,23 +1648,23 @@
         <v>7</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C46" s="3" t="s">
         <v>9</v>
       </c>
       <c r="D46" s="4" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="E46" s="4" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="F46" s="4" t="str">
         <f t="shared" si="1"/>
-        <v>252P - 2º ESO - FRACCIONES - EQUIVALENCIA, SIMPLIFICACIÓN Y NÚMEROS RACIONALES</v>
+        <v>254P - 2º ESO - FRACCIONES - RESOLUCIÓN DE PROBLEMAS CON FRACCIONES</v>
       </c>
       <c r="G46" s="3">
-        <v>15</v>
+        <v>20</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.3">
@@ -1680,113 +1672,57 @@
         <v>12</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C47" s="3" t="s">
         <v>9</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="E47" s="4" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="F47" s="4" t="str">
         <f t="shared" si="1"/>
-        <v>252F - 2º ESO - FRACCIONES - EQUIVALENCIA, SIMPLIFICACIÓN Y NÚMEROS RACIONALES</v>
+        <v>254F - 2º ESO - FRACCIONES - RESOLUCIÓN DE PROBLEMAS CON FRACCIONES</v>
       </c>
       <c r="G47" s="3"/>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A48" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B48" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="C48" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D48" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="E48" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="F48" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v>253P - 2º ESO - FRACCIONES - OPERACIONES CON FRACCIONES</v>
-      </c>
-      <c r="G48" s="3">
-        <v>15</v>
-      </c>
+      <c r="A48" s="3"/>
+      <c r="B48" s="3"/>
+      <c r="C48" s="3"/>
+      <c r="D48" s="4"/>
+      <c r="E48" s="4"/>
+      <c r="F48" s="4"/>
+      <c r="G48" s="3"/>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A49" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B49" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="C49" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D49" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="E49" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="F49" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v>253F - 2º ESO - FRACCIONES - OPERACIONES CON FRACCIONES</v>
-      </c>
+      <c r="A49" s="3"/>
+      <c r="B49" s="3"/>
+      <c r="C49" s="3"/>
+      <c r="D49" s="4"/>
+      <c r="E49" s="4"/>
+      <c r="F49" s="4"/>
       <c r="G49" s="3"/>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A50" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B50" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="C50" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D50" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="E50" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="F50" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v>254P - 2º ESO - FRACCIONES - RESOLUCIÓN DE PROBLEMAS CON FRACCIONES</v>
-      </c>
-      <c r="G50" s="3">
-        <v>20</v>
-      </c>
+      <c r="A50" s="3"/>
+      <c r="B50" s="3"/>
+      <c r="C50" s="3"/>
+      <c r="D50" s="4"/>
+      <c r="E50" s="4"/>
+      <c r="F50" s="4"/>
+      <c r="G50" s="3"/>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A51" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B51" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="C51" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D51" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="E51" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="F51" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v>254F - 2º ESO - FRACCIONES - RESOLUCIÓN DE PROBLEMAS CON FRACCIONES</v>
-      </c>
+      <c r="A51" s="3"/>
+      <c r="B51" s="3"/>
+      <c r="C51" s="3"/>
+      <c r="D51" s="4"/>
+      <c r="E51" s="4"/>
+      <c r="F51" s="4"/>
       <c r="G51" s="3"/>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.3">
@@ -2257,44 +2193,8 @@
       <c r="F103" s="4"/>
       <c r="G103" s="3"/>
     </row>
-    <row r="104" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A104" s="3"/>
-      <c r="B104" s="3"/>
-      <c r="C104" s="3"/>
-      <c r="D104" s="4"/>
-      <c r="E104" s="4"/>
-      <c r="F104" s="4"/>
-      <c r="G104" s="3"/>
-    </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A105" s="3"/>
-      <c r="B105" s="3"/>
-      <c r="C105" s="3"/>
-      <c r="D105" s="4"/>
-      <c r="E105" s="4"/>
-      <c r="F105" s="4"/>
-      <c r="G105" s="3"/>
-    </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A106" s="3"/>
-      <c r="B106" s="3"/>
-      <c r="C106" s="3"/>
-      <c r="D106" s="4"/>
-      <c r="E106" s="4"/>
-      <c r="F106" s="4"/>
-      <c r="G106" s="3"/>
-    </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A107" s="3"/>
-      <c r="B107" s="3"/>
-      <c r="C107" s="3"/>
-      <c r="D107" s="4"/>
-      <c r="E107" s="4"/>
-      <c r="F107" s="4"/>
-      <c r="G107" s="3"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:G107" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:G103" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <conditionalFormatting sqref="G1:G1048576">
     <cfRule type="containsBlanks" dxfId="0" priority="1">
       <formula>LEN(TRIM(G1))=0</formula>
